--- a/assets/files/templates/SafePlum_confined_space.xlsx
+++ b/assets/files/templates/SafePlum_confined_space.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="127">
   <si>
     <t xml:space="preserve">밀폐공간 작업 양식 — 작성 안내</t>
   </si>
@@ -2770,9 +2770,6 @@
     <t xml:space="preserve">후속 조치</t>
   </si>
   <si>
-    <t xml:space="preserve">09:05</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -4342,9 +4339,6 @@
     <t xml:space="preserve">측정자 성명</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-27 09:05</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <i val="true"/>
@@ -4536,12 +4530,6 @@
   </si>
   <si>
     <t xml:space="preserve">환경팀</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">09:58</t>
   </si>
   <si>
     <t xml:space="preserve">적정</t>
@@ -5013,9 +5001,6 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-20</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <b val="true"/>
@@ -5267,9 +5252,6 @@
   </si>
   <si>
     <t xml:space="preserve">확인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-15</t>
   </si>
   <si>
     <r>
@@ -6506,11 +6488,11 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="16" t="n">
+        <v>0.378472222222222</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>48</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>49</v>
       </c>
       <c r="C20" s="18" t="n">
         <v>20.8</v>
@@ -6529,7 +6511,7 @@
         <v>적정</v>
       </c>
       <c r="H20" s="17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6573,7 +6555,7 @@
     </row>
     <row r="24" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="21" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B24" s="21"/>
       <c r="C24" s="21"/>
@@ -6585,7 +6567,7 @@
     </row>
     <row r="26" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B26" s="10"/>
       <c r="C26" s="10"/>
@@ -6597,12 +6579,12 @@
     </row>
     <row r="27" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B27" s="11"/>
       <c r="C27" s="11"/>
       <c r="D27" s="11" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E27" s="11" t="s">
         <v>47</v>
@@ -6613,15 +6595,15 @@
     </row>
     <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="22" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B28" s="22"/>
       <c r="C28" s="22"/>
       <c r="D28" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="E28" s="12" t="s">
         <v>56</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>57</v>
       </c>
       <c r="F28" s="12"/>
       <c r="G28" s="12"/>
@@ -6629,7 +6611,7 @@
     </row>
     <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="22" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B29" s="22"/>
       <c r="C29" s="22"/>
@@ -6641,15 +6623,15 @@
     </row>
     <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B30" s="22"/>
       <c r="C30" s="22"/>
       <c r="D30" s="17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E30" s="12" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="F30" s="12"/>
       <c r="G30" s="12"/>
@@ -6657,7 +6639,7 @@
     </row>
     <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="22" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
@@ -6669,7 +6651,7 @@
     </row>
     <row r="33" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B33" s="10"/>
       <c r="C33" s="10"/>
@@ -6682,41 +6664,41 @@
     <row r="34" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="25"/>
       <c r="B34" s="26" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C34" s="26"/>
       <c r="D34" s="25"/>
       <c r="E34" s="26" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F34" s="26"/>
       <c r="G34" s="25"/>
       <c r="H34" s="26" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="25"/>
       <c r="B35" s="26" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C35" s="26"/>
       <c r="D35" s="25"/>
       <c r="E35" s="26" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F35" s="26"/>
       <c r="G35" s="25"/>
       <c r="H35" s="26" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" s="12" t="s">
         <v>69</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>70</v>
       </c>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
@@ -6727,7 +6709,7 @@
     </row>
     <row r="38" customFormat="false" ht="16.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B38" s="10"/>
       <c r="C38" s="10"/>
@@ -6739,25 +6721,25 @@
     </row>
     <row r="39" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B39" s="12" t="s">
         <v>72</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>73</v>
       </c>
       <c r="C39" s="12"/>
       <c r="D39" s="12"/>
       <c r="E39" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F39" s="12" t="s">
         <v>74</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>75</v>
       </c>
       <c r="G39" s="12"/>
       <c r="H39" s="12"/>
     </row>
     <row r="40" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="27" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B40" s="27"/>
       <c r="C40" s="27"/>
@@ -6769,7 +6751,7 @@
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="28" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B42" s="28"/>
       <c r="C42" s="28"/>
@@ -6903,7 +6885,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -6916,7 +6898,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -6929,7 +6911,7 @@
     </row>
     <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="28" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
@@ -6945,16 +6927,16 @@
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>80</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="11" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="11" t="s">
         <v>82</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>83</v>
       </c>
       <c r="E4" s="11" t="s">
         <v>41</v>
@@ -6966,36 +6948,36 @@
         <v>43</v>
       </c>
       <c r="H4" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="I4" s="11" t="s">
         <v>84</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>85</v>
       </c>
       <c r="J4" s="11" t="s">
         <v>46</v>
       </c>
       <c r="K4" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="L4" s="11" t="s">
         <v>86</v>
-      </c>
-      <c r="L4" s="11" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="30" t="s">
+      <c r="B5" s="30" t="n">
+        <v>46322.3784722222</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" s="17" t="s">
         <v>88</v>
       </c>
-      <c r="C5" s="17" t="s">
-        <v>89</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>90</v>
-      </c>
       <c r="E5" s="17" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F5" s="17" t="n">
         <v>20.8</v>
@@ -7014,10 +6996,10 @@
         <v>적정</v>
       </c>
       <c r="K5" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L5" s="18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7814,7 +7796,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7826,7 +7808,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -7838,7 +7820,7 @@
     </row>
     <row r="4" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B4" s="11"/>
       <c r="C4" s="24"/>
@@ -7852,7 +7834,7 @@
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>32</v>
@@ -7861,19 +7843,19 @@
         <v>33</v>
       </c>
       <c r="D6" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="G6" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="H6" s="11" t="s">
         <v>97</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7881,26 +7863,26 @@
         <v>1</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="E7" s="16" t="s">
-        <v>102</v>
+        <v>98</v>
+      </c>
+      <c r="D7" s="16" t="n">
+        <v>0.383333333333333</v>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>0.415277777777778</v>
       </c>
       <c r="F7" s="32" t="n">
         <f aca="false">IF(OR(D7="",E7=""),IF(D7&lt;&gt;"","작업 중",""),E7-D7)</f>
         <v>0.0319444444444444</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="H7" s="18" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8265,7 +8247,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B33" s="11"/>
       <c r="C33" s="11"/>
@@ -8274,7 +8256,7 @@
         <v>1</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="F33" s="11"/>
       <c r="G33" s="34" t="n">
@@ -8332,7 +8314,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8345,7 +8327,7 @@
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -8358,31 +8340,31 @@
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>41</v>
       </c>
       <c r="D4" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="H4" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="I4" s="11" t="s">
         <v>111</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>112</v>
-      </c>
-      <c r="G4" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="H4" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8390,25 +8372,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>100</v>
-      </c>
-      <c r="H5" s="35" t="s">
-        <v>120</v>
+        <v>98</v>
+      </c>
+      <c r="H5" s="35" t="n">
+        <v>46315</v>
       </c>
       <c r="I5" s="15"/>
     </row>
@@ -8596,7 +8578,7 @@
     </row>
     <row r="21" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="38" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B21" s="38"/>
       <c r="C21" s="38"/>
@@ -8609,49 +8591,49 @@
     </row>
     <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="29" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B22" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="G22" s="11" t="s">
         <v>122</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D22" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>126</v>
-      </c>
-      <c r="G22" s="11" t="s">
-        <v>127</v>
       </c>
       <c r="H22" s="11"/>
       <c r="I22" s="11" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="B23" s="35" t="s">
-        <v>129</v>
+      <c r="B23" s="35" t="n">
+        <v>46310</v>
       </c>
       <c r="C23" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="G23" s="39" t="n">
         <f aca="false">IF(B23="","",EDATE(B23,6))</f>

--- a/assets/files/templates/SafePlum_confined_space.xlsx
+++ b/assets/files/templates/SafePlum_confined_space.xlsx
@@ -6174,22 +6174,22 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
         <v>7</v>
       </c>
@@ -6202,17 +6202,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
